--- a/catalog/近十年文献总表_镁铝钛与镁基复合材料.xlsx
+++ b/catalog/近十年文献总表_镁铝钛与镁基复合材料.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文献总表" sheetId="1" r:id="Rb1f5c837f4e74524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="2" r:id="R2e35303902b94181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文献总表" sheetId="1" r:id="R7ceb54543baf45d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="检索说明" sheetId="2" r:id="R3da64a70d1234f76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -913,7 +913,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P13" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对17页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对17页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="60" customHeight="1">
@@ -1413,7 +1413,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P23" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对38页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对38页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="60" customHeight="1">
@@ -1813,7 +1813,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P31" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对26页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对26页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="60" customHeight="1">
@@ -2013,7 +2013,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P35" s="9" t="str">
-        <x:v>作者未在DOI记录中登记，正式引用前补核；主题和材料标签按题名归纳，细节以原文为准；全文已核对17页（仅本地保存）</x:v>
+        <x:v>作者未在DOI记录中登记，正式引用前补核；主题和材料标签按题名归纳，细节以原文为准；全文已核对17页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="60" customHeight="1">
@@ -2063,7 +2063,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P36" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对19页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对19页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="60" customHeight="1">
@@ -2513,7 +2513,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P45" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对25页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对25页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="60" customHeight="1">
@@ -2713,7 +2713,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P49" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对10页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对10页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="60" customHeight="1">
@@ -2963,7 +2963,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P54" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对14页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对14页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="60" customHeight="1">
@@ -3113,7 +3113,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P57" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对7页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对7页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="60" customHeight="1">
@@ -3163,7 +3163,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P58" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对11页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对11页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="60" customHeight="1">
@@ -3213,7 +3213,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P59" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对11页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对11页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="60" customHeight="1">
@@ -3363,7 +3363,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P62" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对14页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对14页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="60" customHeight="1">
@@ -3413,7 +3413,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P63" s="9" t="str">
-        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对11页（仅本地保存）</x:v>
+        <x:v>主题和材料标签按题名归纳，细节以原文为准；全文已核对11页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="60" customHeight="1">
@@ -7513,7 +7513,7 @@
         <x:v>题录来源</x:v>
       </x:c>
       <x:c r="P145" s="9" t="str">
-        <x:v>作者、年份及页码据期刊机构存档补齐；主题标签按题名归纳；全文已核对6页（仅本地保存）</x:v>
+        <x:v>作者、年份及页码据期刊机构存档补齐；主题标签按题名归纳；全文已核对6页（PDF已同步；开放许可未核实）</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="60" customHeight="1">
@@ -14821,582 +14821,582 @@
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="优先阅读"/>
   </x:conditionalFormatting>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="Rd5ba6fcfd6ae4cc4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="R451199b464cd443b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="R2b3dfef9d1ee4704"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="R19887bc1a20647a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="R4e1d6f584f014d8d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="Ra66a624e31c74e38"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="Ra6fd95fa067f4801"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="R0f63117a85bf4f39"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="Rb2de3bbeb8fb478e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="Ra648803ada914d43"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="R6004db95b7754347"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="Rb39e422c3ba14fdc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="R21074c50df0f4934"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="R5ecf414026014cda"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="R24c11a30a56e461f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="R2aaef54d0358439b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="R709c98d95c00487f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="R450a51a92578452c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="Raf3d99a20f8e4e3d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="R7422f9df7a3f49f9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="R0edb6cffa70d4e0f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="R2b2542bec17940d7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="R5bde83a67bba4bcb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="Rcb408005ea894ed0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="R823b4d4e5738434c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="R6477ae5ee5db4edc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="R16f4d2a541e64f6f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="R1a974792b5ea4871"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="R903b487d5b334ef0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="R72a19716027f4dc0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="Rb373d553fc4d4bf0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="R0730a5be941c4caf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="R55b599c7cd6a4a78"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="R1eada7b7003a4ef9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="R85bda0bde27b4aec"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="R896c241ae22942ff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="R5a786e043a1449f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="Rd8564e3e162c4f5f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="Rd181054523494184"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="R2e3ec42928b14105"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="Rcfc323cbeb804bc0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="R4aebeeb3018c4b86"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="R3ef1d83417cd4393"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="R7e85fd48cd714db3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="R7b761a9678524a66"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="R3c16461d04dd49a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="R8bd2499d275e4174"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="R4ffe1ad1cf1448d0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="R90b7eb35c595406d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="R67298e779b194cad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="Rb2ae24bd6277405a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="Rfb9148f4861841b0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="R6db77e9227434553"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="Rf1a010d22b444665"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="Re0c533ef98334a80"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="R4dfa6d201343483b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="R3ead0f9da47d414b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="R945054f272404e88"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="R933dd4911d914f5d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="R7ddb3b2e502a4247"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="R7b870ad9323d4136"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="Rd868b09a60924b94"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="Rd4d4b629dc414087"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="R6ff0075998404ce5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="R54dbbeafeabf40b1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="Rcd8b1e8f7e80484a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="R2b4018918aa0432a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="Rbfef1f85a3f64c5d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="Re79e6f117c254474"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="Rf0d26a316de84471"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="Rc4aef424200c49ac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="R95c15fcc152841fa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="Refb760874e614e0b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="R0172d40ec7d24a86"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="R148cfe757c63460a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="Ra2b0078a36054fa7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="R29e301e1fb5746b1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="R38452dd56a34440e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="R4a6172f0c9124f6a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="R0e84ac6184114b82"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="Ra90b4f2584ee4250"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="Rf0dd43e244f84b31"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="Rc9f022cf520d4f20"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="Rdc479c604481469e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="R9d6d8fc86cfa447d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="R9ec8c1009440454d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="Rdbf105a1b75848b6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="Re5f18d1c95d64654"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="R082f4a731dc446f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="R49c150e901f74e94"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="R24143f66b3ba4f16"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="Rd2e8f0c6284a40d9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="Ra5647a8bfec04e56"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="Ra65baa5c5ea84f3a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="Ra506654063ae43e9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="R82338255844840b2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="Rd331c180875a4bfb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="R74095ed982554c20"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="Re83b1a1d6a064753"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="R6ca68cb1de7c4879"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="R51f589c3140b444e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="Rf970e02020204f69"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="R213508927b004207"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="R5fab019cb17b4dc0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="R8c8e22785ac84ba7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="R524b4c7e1dac4643"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="Rf7737fa7ab994ab3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="Rcb856cd82a834669"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="R0a6d646f106147d0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="Rf0f0303ab970430d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="R6908d37c96b7460a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="R64fb5834184a4f66"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="Reb262c9934bb4cf0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="R98775d55caa64b0c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="Rf824d3912b064c55"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="Ra6a2c0d64d6c4b5e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="R7778c5eea0414d61"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="R608cf98ffea54460"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="Rd8e0caba94b44f92"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="Rd4d8d4af9e5245b8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="Re132a4baf4214d0c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="Rcd2068b75d354edc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="Ra20fd0474e7f4a27"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="R161bf6a2fc1e4585"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="R60d5298551cb4f55"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="R9364975da8364a77"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="R4f97d263eae6465f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="R418350b0c60b42a7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="Ra2080a3083654cfa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="R9d2645f99e734749"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="Rbef4007cf4714937"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="R094b811ff01448a5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="R6a2226f923434c29"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="Rda4f8d2d2af04f8e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="R0ab1fe07b04c4ffc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="Rc4300a5080344e8a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="Rce40090ddfd34f9d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="R9b3e99bebd7244a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="R8754f7fed2324368"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="R19b2bed358eb46ac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="R811f4642396d481e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="Rdcdfbdedd50d4054"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="Rfa27f490e6ad4b9c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="Rad1e7f8fdbe545be"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="Rd8f9e01ff0e74016"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="R6acdb367a998411e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="R999754c3405948d8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="Rb719a760e31f4c8b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="Rf20449dc255e4470"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="Rdf4035328c6040a3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="R0dc7e6b653b34762"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="R5c5f0cabed5f4115"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="Rc593892b6c74414d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="R5caddfd72ab04868"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="R422b982be4ba4d02"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="Rab8bd2b3121342f4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="Rc4b14a7164e0443d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="Rdcf9e78877f14319"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="Re22e1c7341274c3e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="R01a8a9a8df974cda"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="R2eac24f759f948ec"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="R5c51542d51464a00"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="R978dd603326843ed"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="R3c78fff7c60043f3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="R1ef77e1ecb394d08"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="R88f7f9b02b284691"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="R0f5928ebbf9a4db6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="Rb585d0184a2b4cf3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="Ra7b317b321154200"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="Rfbb3dbaad64c4316"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="R172db618b74e4086"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="Rfc314f490a6b481e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="R3250b759e33b4e8a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="R0b7e5ecf91214cf4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="R7232f1546fb748c7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="R2bfe8eb41c424f3d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="R278b79e01bb24816"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="R8c95229173034027"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="R3922c72fe5fd4773"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="Raecb16bb62ab4205"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="Rf958965b96c1452e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="R801898fb75d44997"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="R98dadb92c6274ad7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="R8ab8e4a3f12d40fe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="R3d529026e0134dce"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="R0e57731e52fb446a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="R25898813cf2d4e86"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="R8a88a3a6573a4d8c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="Re572af270751400c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="R182528b1a9e3428d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="R8105736ac4c24d85"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="R224ffd37118a4062"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="R39284e1aab564597"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="R11bc06ed083148c0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="R735777f1651e4ec2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="R6037122a65374183"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="Rded50f1b4269403e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="R8f6dd59c637046a3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="R250e95bd4e8041e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="Rc0c94d50548643ad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="R3f53f28390d549c8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="Rd6c9d03e9305419b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="R5ecf9c8caadd4bc8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="R065a519c0de045d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="Rde860d7b12624006"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="R7fc2893c8cef434e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="R2988337c65ad4e9e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="R9774ab5fb423492f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="Rc294f39c81a94ab9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="R66651b2367364669"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="Rd96420b8fca74024"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="R773de3c6148040d2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="R4330e0736f0b412c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="R8091352bb1994ece"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="R8530cde807184fcd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="R4ec20fbf99c64fbc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="R931b45c670e443a4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="R68db5bc9c84c40e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="R725847c119e245b4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="Rdeb5dd2d1d23459a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="R15b76a3085414f4e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="R5f4c9427e7944440"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="Rb7f02ab595f9405d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="R6e45bbcd038e4b53"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="R9a745dfc204a4908"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="Reac32f84120a45f5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="Ra98dd5ca1bf44669"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="R7ca7161632924d43"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="R0ef7230796aa44aa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="R5fd0b8e63c3b4960"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="R028e1b989ea6431c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="R7067d073919b4892"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="Rb7a35a9ed68d4d4d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="Ra2030f9fe27a4f9d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="Rd55ad272b50c4a7c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="R19c8e07e6e7041b9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="Rd9d3d4d77e0144a8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="R5715162f01b249ec"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="R6b03944e4faa4997"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="R5ba6e1af399b426c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="Rd367b0c2d7d04953"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="Rded1f14f24de45c3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="R531fa95a33b44cda"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="Ra5ab8293bae54f55"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="R4726117f7fec43e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="Rf7fca7b310254994"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="Ra7a0eba8cde7479b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="R2d8b56a0cf8644bd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="R79f538f094e1458e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="R928a9bdcc02f4682"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="Ra87f7ee6c3ac4d8d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="R1d9b168364844703"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="Re69fadb7b6964f86"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="R0b54a9c37e7b413c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="R2e24c00f8ecf472c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="R592f8ba4a78c4c3e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="Rb0051f73a75c489a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="Rfccd21ba499e485d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="R61174804328f4e06"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="Re228b4f19ab34f6d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="Rf89b3e96ca7343bf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="R0641c23cbf614dd4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="R7434a91b102545d8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="R345d20c8fe034ac0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="Rfcd0f2f75cbe4c78"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="R41c3d72603cb4c4c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="Rc2e41f43fc5a4d5f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="Rf1416159ff944825"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="R5cf728e3a46542ae"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="R00f42a9a05d543ed"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="Ra7836fd269464974"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="R4028d5bb07ed4b2d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="R6f2234db14894f59"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="Rf028735713f84394"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="R3560244f86fb45e8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="Re5a1d42eed0644b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="R19fa29ad0cde4ab3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="Rb5742f89136a4a3e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="R3bc2246a53f64750"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="R5176ad6f2d824405"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="Rcc1d7c10d9664a97"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="Rcedeef05de9e48f6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="R5821b79d0f1e4093"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="Refd287ca45b44796"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="Rf382c106c2c64fcb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="Rd2fe85f4806c4697"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="R4d23757f02a544cb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="R7fe3f5023cab4137"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="Ra504a6ee72e24818"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="R50fea02147eb4188"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="Ra110e40c89f94165"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="R283fd00b393a410f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="R1b4181568df14765"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="R39028ac3a4a44bf0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="Rac2648c4a4df42b9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="R858ee264baf24641"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="R9af615caaa0846dd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="R656a1b20f7184ba9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="Re9e7501dd95745ba"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="R6f534620dd124139"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="Re1cac52a28b84be0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="Ra115a75b96564bf9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="Rec51bc931b3942f3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="R9f310fe9064549e1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="Rff9508637f074f81"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="Rdc4007024e3b4b2e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="R10bbfe70b5724691"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="R29643257ceaf4ae7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="R354f9f4713504bfc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="R1f8424a1d01d4265"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="R6917c29673f0446a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="R8f2657723f3c4403"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="R0bfca9d6bd0f44a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="Rf3ece01af4d243e7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="Ref752d7d7784417e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="Rd563ed95ad4a4924"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="Red73ab4bc99b4588"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="R81aa1667776b4c61"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="Rda924318d4604382"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="Rc03b484673ac4a73"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="R72c5a89972004b07"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="R507525b737e44d2d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="R17d799714f6d4e5d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="Rc843e73511be4b9a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="Rbade73e4a5d84d91"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="Re3cdfcf017474e69"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="Rdbe9ead2ca85453e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="R6729228cf5e74459"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="R3983ffa2d94c4d19"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="Rf96718eb978640ff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="R30b0b5b609f74731"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="R42624c83adcc4b1e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="Re4b06e9d54254d4e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="R0669658e8bc5428b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="Rb66dbd86096a414c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="R457620cd711f4db3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="R6d3d10e9f0dd4a65"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="Rab29aa63e0f4459b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="Re0201d5fe9d6462e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="Rb12881c6cb284d2e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="R9801564460fc4654"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="R2bc9b0c8e6e2416f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="R8b7596ff9ef840ac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="Rdc866d56d7034027"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="Ra71b374f735d48f8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="Rb14aca21cefc4733"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="R038a092c26cc4a08"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="R64562b48bbe74cd9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="R063ec926cd2c4028"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="Rbdd75c5516534193"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="R0808e00f90a442b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="R3f87b778a01b48ed"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="R2a989966ce2640ab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="R4e3a934daeb04387"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="Rcf4026bca4c0428a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="R8cb47bd8abbc46b6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="R370b6363e0e24b7c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="Rcaf9376ab4524811"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="Rc832bf69abd64db1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="R88899354083d4cb2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="R78c1dbea2a624e4a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="R4e1f636754904dbd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="R60fc7e38bda24212"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="R3ea1e213f8e54c35"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="R886732c089b544cb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="R025bf78ca14b413c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="R94e6be6ad2244125"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="R49f1f8ad19174183"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="Rdcdda1c65f8c436a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="R6e41880288684957"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="R41549ea610f640f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="R6c7d5dadc1a44ac2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="R7eb5bacc11b5488d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="R82458df7fce14855"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="R3742392717034df5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="Rb4dcd92120ab4d8e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="R92243a7f1c59426c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="Rfe39c7e53aa349e7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="Rb8a572934f304c24"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="Rf0faee40729f4da4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="Rfb1f7832e90d4100"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="Re603c43eddb24a7f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="R1f1a7af775124712"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="R42729ce3191f4f34"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="R84081c5ec3764a96"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="R807787dc1c8b492a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="Rb1179a9e01d94eeb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="R77695ac3f2764195"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="Rd014dc4a7063424c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="Re47ee18fe19e4c88"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="R44b2b963d9d24643"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="Rc710cfdb8bba4f81"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="R258da67460014b1a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="Rcd575f9e752049c4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="R96cd80243c3d4fa9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="R18ee3b3be00b4eb4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="R31755d1d37b74b12"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="Rd6ff285429784dff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="R2b844b2d90364a1e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="R4f7d23f11ea649a8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="R015c24e9c558472d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="R90e43badde5241e1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="R4e4f950ee81b40dd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="R35bf9a2c5f734bcf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="R9a2d76c303604e49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="R42f43399b7064b58"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="Ra4afbdebc5114f76"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="R6aa8465d47194e75"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="R476968b2c1874ca8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="R822032ea7ff7469c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="R19608ba7d0904213"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="R278483bea45c4157"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="Rf19b9269f4de475e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="R174d8f1001954d9c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="R912269cbaddd4dc4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="R115acacd65f04195"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="R566577d7c00644fe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="Reb9cdfe5e6ee443f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="R429b2c1e9a454a1b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="Re2fa56bf042e429e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="R75def4f71d924dc1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="R63fc6652b9e04d2f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="Rbb9bc7463d764ecb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="Rf3b9c758930a4c96"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="R864c161e94af4dad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="R24dc6a68725b4420"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="R08d2b797b5584bc0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="Rb35ce77831494479"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="R486975443cbe4e19"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="R32e8c19b5dc94e77"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="R41503981553b4deb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="R0aca1b803971407d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="R1f59cdf99d1d4050"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="R252418078d894be7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="Ra0f7f0f528894a1e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="R441265bf6e7f48d7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="Rf308d9719f794ed6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="Ra7235a2ef8934736"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="Rcd9d083642ec4c41"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="R0c8be8fd061f4d49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="R7200e840ac2e4c22"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="R9e88c3464d404045"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="Re2729b7ca40c4944"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="R4cf4fa4b552a4883"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="Rde5f1e4af7534c01"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="R02a740dad3b74d7a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="Rcbf8bbd2713b43eb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="R3458a69139664373"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="R58026d3e15f04990"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="R6844cdf0a4b7435c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="Ra5ff2e184dbc4da1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="Rb4c809ab7c274b61"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="R2938c283ab34421a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="Re50d175b4fa34a85"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="R90e85c3b9e174ac1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="R043f23ba20b542f9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="R50ad07ea1afe4f9e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="Rddd07f41f36d405b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="Ra74e5d809b5e4552"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="R1334d262ee7e4cf5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="Rd22e57f733e94bb9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="Rd2d538a3a2cc474e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="R0ba3e11db43c4d89"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="R6802f74cf38f47c3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="R92a6279d2fd04162"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="Rdf7b24e230fd45e6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="R14e62af6ce3e445b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="R93abb7c9086048e0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="R2c57fa3ae9bf4314"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="Rff504f724ea64637"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="R58ad9b7be5be4b83"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="R696947dae36140ff"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="R40f1f1c5baa9469b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="Rbf6023bcb35749f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="R13fd537e3e1248fc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="R6d20ea15d8614f86"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="R07646f531de74d71"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="Rc7f5d8fbe1944432"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="Re886fc5b3405424a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="R0bb4e496140b4816"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="Rf4a4d4d2f0f54fb1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="R8934b471f1b14a9a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="Rb5154d29158645f6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="R6f5c020ed72c4657"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="Re42a1318f8a841b9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="Rf947fe5a482e4d25"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="Rf8c54a5028d841f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="R08a452b61dd04383"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="Rcac8814b9b104ddf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="Re57816e90da34812"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="R9f00e603041c440b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="R84f994c1798a4547"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="Rb76338faa83c427c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="R308bf76ccbfc46b7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="Rbc0c4b3bf94446f3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="R2431e16aca10448e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="R47fee8cfdd7d4a36"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="Rc574e5a135054b7f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="R6969b80cb9ee4f4f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="R44a430ef812a460e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="R991fb9d3e4384df0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="R15a965c5cc514ca1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="Rbae05b9e984d4494"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="Ra4cab68d3a074f0e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="R6080220b9cd54a27"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="R01339dfeaa2646df"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="R5bc9b1cb85834e13"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="R9d20105f99d24842"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="R2e93628907e44725"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="Re258ace1d3a04b85"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="R15d42636ed474ade"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="Re4a177e543524df9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="R77e35efa7d194333"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="Re9a452218d174010"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="Raac17298def34a13"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="R70b588a692904f56"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="R1839e84c28f748ab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="R15bc9c2c9d674239"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="R6f1ccb9aea144e52"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="R71830c9d0bf949f1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="Rfa4469955fb946da"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="R702bac7167824a2c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="R322e1fe917174e20"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="Re90083238e344b93"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="R0affe269659646ad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="Rc7f202f850a9475d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="Rfd62ff69778b4d87"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="Rcc5021498b374a68"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="R7348587024984868"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="Rd921b9d124da4f23"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="R6ca2e2825ba343e3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="R4bd0b61dad0741dd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="R4d95c0005498430f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="R44143ab6dd8d49f8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="R4a39e19f9f8d43f0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="R4fa7a121b3874bf8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="Rc9cc92d5e18c4fa1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="R19080c1c4879418c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="R4705826d69b44c68"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="R59585aff9f4c4f32"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="Rdaa8b778cf864eea"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="R49cd3be97ce14459"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="Rbdd02324ddd54d50"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="R965a27c81696497d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="R76bfcc1a5b8543fc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="Rba5414cfa7b54ebb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="R7ca05e4630ae4a94"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="Ra6e182b2b1584fe4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="R3d74b085b4ad4829"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="R889d2a53449a4ba9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="R753ed8eb8b0746c5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="Rfd7631967ac442aa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="Re682111dd7244bcc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="R3cba8914d6b140bf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="R6f33ea99b1214ee2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="R1f7b0c0aee85482c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="Rf386f43a0e9a4257"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="R498d70c0b8744767"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="Ra1f8188585684813"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="Rfb69ecc270e549c0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="R38e95cc563774b61"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="Ree1e62651ce34945"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" r:id="R6b7cac98f6f44907"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="R0808506cd5ac4dfc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="R2d913e8ad1d64b60"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="Rb84b7959c3d74026"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" r:id="R1f40a0bbf8704151"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="Rf331ad6cdef04349"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" r:id="R50de463d4b50401a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="Rd641dd790bb340fb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" r:id="R1edf3511fdad4cab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="Rd45fe4b3ef774a30"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="Rbf068a852a0a4017"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="R8b9142a4bf4d4dc9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="Rebf566f269864a00"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="Racd94b49ae074c16"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="R57c447cf329c413d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="R2010407c7ae246ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="R56831989403a4e9b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="R0475e28b49f44272"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="Ra501254f2f3c48e5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="Rc80f5defb3d64e06"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="R766a7b10d63d4783"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="R0c0505083ed34e93"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="R0f494744d31c41ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="R1e771cd9899b45f7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="R65946e158eb44fc6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="R4fa7524128cf455a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="R96e46cbe19644e7c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="R04d3ce62aa644d69"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="Re91f8b22d3984d18"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="R123d3878fe084572"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="Rdfaf5ad7699a4fbb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="R9c630e8bf3624aca"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="R84708b781b584782"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="R1070eb851ff24772"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="Re5896517a2e84c0e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="R419e51d726814fd9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="R33734c1a225d46d0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="R23dc2715cec54fcd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="Rcb35f6c073884dca"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="Rd807892c651042dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="Raaae078951c1438b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="R9294192c2f914aa6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="R2045e5f5626e4dc5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="R2783be6742c5479e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="R7279f8e33ec149f0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="R1e72a77baf284f6d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="Rb51bd892ee924cf2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="R7ff30aecbc344ab6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="R59f7302540074cd8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="R52ef2e150367428b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="R2ab7a68cb99b4dee"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="R7d397bbab4534b74"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="Rcf212acb40e54602"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="Rcc330e207d404ad9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="Rc797561a0d414f21"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="R8b8b9cf25ce34ae3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="Rabd10cf08bc74ddb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="Rce298e444b43472a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="R42f1eade6d0c4097"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O30" r:id="R5b6ef80b565442a6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="R05b3300070e647f5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="R95bfcb24d9cc48a7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="Rc58740124d4047d9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="Rdefbffcfeba04849"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="R2bafbb5ec65b44ce"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="R352bd71180e9485b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="R2a3b89af6b924013"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="R511b35641e424fdb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="Rfb3d7a66fa204461"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="R86e7324ca66e4455"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="Rc46294e369104b15"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="Rdc6af33840984266"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="Rcc77d34b56e1419f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="Rd88a7513debb4fa4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="R145c0553e42e4b5e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="R670d40fabfb14501"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="Re08aea48c4b94695"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O39" r:id="R8dbaa8e5c0ff4be0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="R07e4a3bf2dc4495e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O40" r:id="R85b25a6588b24798"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="Rf4475c1888d04ac1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="Re955105d2c924554"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="Ra47b501b0de645ed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="R7660ceb558c84d28"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="R47134927d2084cbf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O43" r:id="R23f623526cec4640"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="R0f7053bdcc4b48a7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="R6be205549eec44f5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="R3899023b0c324bea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O45" r:id="Rb7ab341abf034d2d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="R6bfe6a95e9d54bc4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O46" r:id="R4476e71c03b74648"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="Re56e841b28e44a8e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O47" r:id="R8964573cf7794e48"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="Re55cfda6e5584da9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O48" r:id="Reb030e199d3c4371"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="R7c6cbfc31cdf4a3f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="R9e33ca4d80f2416b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="Rab3358f274a7410a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O50" r:id="Rdad213be0371430d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="Rde40147f62fc4c4f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="R43800dd43ff943c3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="Re7ec3e5328f240f9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="Rf030e96919c046fb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="Rb5ca2d6c4e29407d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O53" r:id="R45f9dc1c6eb34e36"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="R1a0887369abe41c3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O54" r:id="Rfa39184624fc43ad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="R73610b5cbd544f25"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="Rba00e87141cc44b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="R225d304ffbb5442e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O56" r:id="Rd1de62b290f14948"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="R1177ee1906b244c1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="R8c70f6b351e64618"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="R8b7c217a79cf4d03"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="R9bf61710d2aa4c5c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="Ra78892d9f13e4529"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="R96e7c008369d44e9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="R02987ad2aa9d4dc8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O60" r:id="Rd748d2f441fd4501"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="R2de918c074354cd1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="R13ce76e483304685"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="R6983bdfb493546f8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="R7415d8a0d3494a1f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="Rb30552d2470d487c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="R549c52ddef004a76"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="R1c5015012b2645d8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="R8bee259100d245de"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="R33ad61083e2c4e1a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="R35bd62ca244f4932"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="Rad62eb57694947cc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="R013a90fa0e7e4c74"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="Racfce1de27064553"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="R43105202b64f460c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="Radcf743ddf914a0f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="R8b82a983bb69489d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="Rde057694c93d4b3e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O69" r:id="Ra0fd2fab3e744223"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="R3020c7b19d774a3a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O70" r:id="R5095630a5b824c11"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="R858ae7a487904965"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="Rceba3a4acb7849ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="Rfb19563c14c34e84"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O72" r:id="R17496f1360ea435b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="Reecca883ce1d4d19"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="Rfe10dd36a81b4fa3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="R98f7f49d8fc04604"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="Rb57f4779563b4093"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="R1b92fb47ad114f46"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="R0b1d812c75a447b9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="Rd779f7b0a09b4597"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="Rd42ae8cd18844809"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="Rabc96410b90b4688"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="R8a3e23487e654395"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="R26e82bf8c0184747"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="Rd2dc118e5f46448c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="R193465f2299b4d2f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="Rbc7bc651fd314cff"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="R832946bc60564c0c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="Rf10de147c7a34271"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="Rbb15a48adfef46d6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="Rede2b8d3b51c4dc3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="Ra123e3a6c80a44e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="Rb5096ecfaa554b5c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="R13dd3b9cd4864596"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="R0f14f2d969014a79"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="R40a3eaf3c7834ebd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="R3682c2906c3a4fb2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="R4996347ab67f40ab"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O85" r:id="Ra155a39b63fd468c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="R75281adc6fcc4aab"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O86" r:id="R14f0a30e2ffb4e53"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="R680e34c5ecb54f80"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="R8ee9581664f44d74"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="R1661d724d0bf46ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="R7c9ee26eeba74197"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="R764491a39e7d42c2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O89" r:id="R97194272f3c74819"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="R510d5b72fd12491f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="Re0f24080fef54032"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="R15660b7d6465400e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="Raec2247a3d9c4d2c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="R029101568a474f41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O92" r:id="R570d5f2b7f21453b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="R27b162524b3441df"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="Rd654d5efc2f245ee"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="Rdc5db1d6556d4893"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O94" r:id="Re3d7351e32424605"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="Rce71c3b366c84f80"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O95" r:id="R04f91b93ccbb47a1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="R2d5e627bf53747e1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O96" r:id="R367bc1fdf48b444c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="R7bc8203f40a84adc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O97" r:id="R01a5e172f28b4f0e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="R4f4c6f55a05f4aeb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O98" r:id="Raac8b7399fff45c4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="R8ae136b2ce2c4c1b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="Recd06fdacded4ce2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="Rc188b180cb1646b0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="R64f0f7cb21934ec9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="R975061133e1343a0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="R64387a48b9644ed6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="Rf5035c4b73c042a6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="R4a79a59f04894399"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="R92e82f1b4f3e4028"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="Rbcf565c3b3a2435a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="Ree0170272a3e403b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="Rac06fb9643e54ff1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="R58f8bbe7ebea43f4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="Rd77d158fedf44df3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="Rf9088549b6994ff8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="R55f80aaa00ff407b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="Re4cc985f74fc4d34"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="Ra32ae877e77e4699"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="R4969230ae91f4bf9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="R29d63499d4454694"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="R45d962cc64044ea1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="Rff961f1a796b4c12"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="Rb1395c55639e4f31"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="R1f2c863f6d3b44f9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="Re17ebfda39ed40c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="R39698ebea66c4ac3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="Re786337555814b3e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="R7e301008159640cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="Raf50de3461d64045"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="R8b90287883e146c7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="Rdfe3e89280514e98"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="R94a57ebe96ef4d2b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="R77f50a4710ec4fcd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="R48d341ed97fd4cf8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="R8425219c272946ee"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="Rdc440a6b12ff47c5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="R1daf2738e76c4aa6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="R63f4ab56a6b143ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="R29ad3d6f58334800"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="Rb6835793db324922"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="R8e26adcd41374e95"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O119" r:id="R9a44e2e309704819"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="R1ee2e5d04fb04cc3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O120" r:id="R5f7cd9e095bc4edc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="R1c8435eb054c4332"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O121" r:id="Rc3b8f0930d284144"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="Re98386158bff4096"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="Rd4a5e5bf93df49ae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="R8e4abd5b7f644d2c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="R7abd3a60cada4b1d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="R55c6e49d511e4438"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="Rab817759a396410a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="R6a39e71e283b4fce"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="Rbaa3d9490b8b4e8e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="Rede3548ab2824619"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="Rf47279cac23643cb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="Ref2fe7811a524e6d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="Rca7d47e031874170"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="R73b25e2fdcf545e3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O128" r:id="Rba02781958d44400"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="Rb1b9150886e548e3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O129" r:id="R5156dde790f44835"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="Rb26d747cec5a44ac"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O130" r:id="R2e6276db11ea4f08"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="R4d7d457680c54e25"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="R99fe24a38dd44f35"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="Rde3e29c9092e4535"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="Rab0b27aabfe74b69"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="Ra55c90232f5042a8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="Rbc6cf09e5dec4f58"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="R2f48cef48172449d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="R53d96f050ba64506"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="Re6712c65afb54634"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="R7af0b91f51254b55"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="R181b80a7db1b4d92"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="Rc0960746280743af"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="R7a13e5ebf79d49c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="R23ecb0e1a70f40fc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="R03d7f2dc8c974887"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O138" r:id="Rbb89b3cb55e24771"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="R93702c94cfa84385"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="Rcae81ba0aecd44e5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="R54668471e4044800"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="R0c8be12afaf54ad5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="R065629145237402a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O141" r:id="Ra02c088fabbe4f97"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="Rd0b8803a948f4f39"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="R1e8955da54d340bd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="Ra4468d4136ea4145"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="R0a8ed308c5cf4a30"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="R054094a126c14621"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="R2a0e329319be4860"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="Reff41a8ad7214188"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O145" r:id="R8547dbd565a94de1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="Rb554702e9bae42bb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="R70954ca208b24af4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="Reb5c06afc1ee4b16"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="Rbb9712d6fe814ba1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="R968919f20a8d407a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="Rca8927a19b954a3d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="Rf5b360f971924901"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O149" r:id="R77e33ab0e9a043a3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="Rc6e7d1e3c4994365"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="Rb4938ec40ce94db5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="Rc4e7a493eae34cd9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="R636403eb43eb4cfe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="R2627aeae29a6427b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="R9d11ac40d45443d8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="R99d1fa604bfe45cc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="R358c5fe1b3084615"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="R3b660a253f0547f6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="Rb8ae88e7533448a2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="R166f9f580d484c85"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="R19833ea825374a93"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="R38f43af58c0b45e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O156" r:id="Rc03cf524c92f4f55"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="R638ca318c6dd4365"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="Ra0b8410b0c3a478b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="R970c0d9c757b49e8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="R6e48e3b173344608"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="R6c605acdf7a54ee1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="Rd6e7af77704f4ffc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="R5386a47b790c4a23"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O160" r:id="R753770a1dcd04614"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="R4b6beeff075c4422"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="R12de14571bce4db8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="Re7e0418ef8ac43ed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="R928a10db835347ac"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="Ra15c466105f74886"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="Ra18479cd3cf849c0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="R7880188738984c36"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O164" r:id="R46e4e4e541204d8f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="R0177d34679cf4d9f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O165" r:id="Rd9e67f424fcc4afe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="R3afe0da64bb2454c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O166" r:id="R264b973b278d4f6c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="Ra4ec38469bd347f4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="R0f45281ea7c14401"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="Ra0c48b5ec6fa42c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="R37b30bca43ff4eea"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="R65ce5ae394e14ddf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O169" r:id="R1c29e6706eee488a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="R619132c2e9c142c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O170" r:id="R360c8a6068574484"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="R3b409f012eef4904"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="R2c69182f201142bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="R2630f76c08d54db7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="R5453d129c23b44df"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="Re46a625ed2b648dd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="R7568c337d2114033"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="Rc1b9398767cc4a77"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="Rac1e0f0a2a0c40ec"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="R853e3a8d20e041c2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="Rdfe950988e0849bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="Rf881119983e34295"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="Re0d6127272c14df0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="R10e388a11b844097"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O177" r:id="R39c84722b3e44a5d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="R52c0c0d2e9834a77"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="R319dde0322534144"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="R7d8c447258494762"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="Ra12ee8c9c1c044ad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="R361e2c96d7984f8f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="Re955cd8617a24319"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="R564e4d72d09d4204"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="R78b14c2508414e65"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="R616279987eb24f3f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="R0f9e4fe3a26342cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="R5c993dabf27a4b6d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="Ra89829ec28c6410f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="R91f29be8e6c2404f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="Rfacd3d4c9ec54f1b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="Rcb418a7a52c14547"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="R8130274fcb67432f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="R93f2ead60e504c83"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O186" r:id="Rf7c60fb2986d488f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="R53344ab130ae4f1f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O187" r:id="R12b45a1ceb834f4f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="Rf763e32c72e94248"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="Ra6897854f5874c21"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="Rc418de8c745946d5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O189" r:id="Re88d5b0757114293"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="R1605d2035b844cf2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O190" r:id="R15cdd538d9984c8d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="Rc829f1636dd64914"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="R9692c2f49d9e460a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="R1ad4dee493154eda"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="Ra0c2935741f14b70"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="R7d9060395c8a4eb5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O193" r:id="R5e17af21e11f4362"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="Rf26e9fa1213943a6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O194" r:id="R295c773728d64613"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="Rf86802b741a842c9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="Rb13c9d5b78754bc1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="Racb2de2f07824812"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="R55fb6a24ab444243"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="R1903cb62864343c4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="R88c1bcc1d2a74199"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="Rc6d67995c86344c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="Re958303869634bae"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="R5d0978b4cf1f4dcd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O199" r:id="R7aacaf3026454a41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="Rea82e95f64d04586"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O200" r:id="R9e378035c7d345a7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="Rf5b6bfe6710d4ef3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O201" r:id="Rea1b3220001c4dbc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="R4bb7c44114d840a2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O202" r:id="R9c872d3112bd49bc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="Rb87d0bd1a3834e7c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="R2a7f6494cfec4823"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="Rb7593fd913c94b31"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="R3784a338d5644b76"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="Ra973cb846ec84f48"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O205" r:id="Ra64675275e844562"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="R05f6169cc4a146c2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="R0eff6b0a4ea34319"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="Ra6de27089d184964"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O207" r:id="R078ece79ae604107"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="R6ef135cbeb414988"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="Rf2e456f19fb04a00"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="R3962a6a5a7db4581"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="R764a5809e26547bd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="R07a93f8798bd427c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="R3dd3df579b4141fd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="R0d20ca2469f54143"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O211" r:id="Rc8c9e4a16dc14faf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="Re8f4c153e2f1436b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="Raf3ac21c07264fde"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="Rb634e861d4c74a0c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="R992b5cfb10814b25"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="R73e8708840014f8d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="R582b1cfda9fa4358"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="R240e003a36b148a6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O215" r:id="Rca37e25bb3974ad3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="Ra1caa745b59f4bfe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="Rac3760494a2b4617"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="R1c0e87cf666548dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="R0f036877468b4fe7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="Rd6054dda3b4d4eef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="R08a245d63df840d0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="R448e70fb249e4471"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="Rfd6ed838247a4f60"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="R9490c12874f34ce8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="Re4898d5105994bfd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="Rdaa9bd2235ec44d0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="R2ec29057d06e4713"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="R07fbe6572c0c44a0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="Rf0d5ccec951047ed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="Re30a66cd01a84bf3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O223" r:id="Re88188b9c8344ee0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="R0f02385644c34a40"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="R49392dc022194cc4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="R04bc66bf3cdb43fc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="R806f264b54f34bed"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="R514edf896092454b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="R502ab6a9c62d4939"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="R86cdb030d8c540cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="R89f1899c0a1745b1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="R37e377d65e874b41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="R6bd31d0bc3854854"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="R01d945c4ef784049"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="Rd13b4ba6b7b047a8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="R4dcb6e604aa34596"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="R789d5874d0944496"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="Rb8e4974c1bb94246"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="Rbd51dd3b4af7445c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="R8e6dda0ac8094a4b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O232" r:id="R77cf124b4cce446b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="Rb69e52e928f14f40"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O233" r:id="R9fd0171774bb4bba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="Rc8e79133a7a6446e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O234" r:id="Rb90ea4d04b4c4acc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="R7d77009811ab40cf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="R661b602e92d64bd7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="R60b5ed2440e54cda"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="Rfa0395f86a6546d2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="R8319cbe3ff2045a4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O237" r:id="Rf19183d311cb4ff5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="Re3dfdd46c4b94a05"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O238" r:id="R2746904c209f4443"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="R2b1194adba074195"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O239" r:id="Rd51747ba2a694b0a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="R444d8ea157bf4164"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="R4b70db7837a94bad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="R49521c5539d6470b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O241" r:id="R5e1b7f09ec824156"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L242" r:id="Re4328f3682b04844"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O242" r:id="R2677d46f4a8048f3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L243" r:id="Rbf3aae9dfdaa41d1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O243" r:id="R8e936134eb794a6b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L244" r:id="R07ff614b45794e29"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="R84012e75227d4083"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L245" r:id="R9cb5b25273b34267"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O245" r:id="R50a9d96c0b4641e5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L246" r:id="Rb8ff46c236b94940"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O246" r:id="R2108f7dc403949f7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L247" r:id="R054db09e6a204b50"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="Rd93815bc086146c3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L248" r:id="Rce50647f1e3e4a3a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O248" r:id="Raabc2919fbea442c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L249" r:id="R120e2f42d6384122"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="Rf1998915883a4960"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L250" r:id="R7cd21136d0494df4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="R83be909b7f7a422f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L251" r:id="Rd40c80a351e1474a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="R9142979f73d4494a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L252" r:id="R9e553530217f4434"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="R52ff90a3f09248e9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L253" r:id="R618adc9852aa45d6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="R03be872b27454ac3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L254" r:id="R8a386e22f335455d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="R9e51549fcf1c47fc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L255" r:id="Rd76cfa0f2ed748b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O255" r:id="R3a475eacb19446f4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L256" r:id="R81075505ac4a43ad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O256" r:id="R9582f443e4e04168"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L257" r:id="Rb17d43efec5f4715"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O257" r:id="Re0f370e6e26b4983"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L258" r:id="R1a15c1b92f894b99"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="Rb26378030eff4dfe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L259" r:id="R10386a42356d4038"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O259" r:id="R05e7ee0da4ff466b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L260" r:id="R237314602e724aee"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="Rc5bf1115df5046b4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L261" r:id="R6a2ca8d318bc4dc1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O261" r:id="R9c89546d1ac7499b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L262" r:id="Rd320ffba407c42e3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="Ra66f37f512a44b24"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L263" r:id="Reb551215218d4a37"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="Rbfb8aaa2975f446d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L264" r:id="R49796989c0944c4c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="Rc8ed4e64d4e343b4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L265" r:id="R0e7864e0bcf54510"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="R82326c5920f14613"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L266" r:id="Rd7a6f99404194806"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="R25b40e6785eb41f4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L267" r:id="R858b875a3b4243a2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="Rfb0225a58cec43c4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L268" r:id="R1be84e4d32764321"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O268" r:id="Rb6d686b126ff47f0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L269" r:id="R1deb23fc9326441f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="R6b6e4acf522b489e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L270" r:id="R64c52f96007b4eb1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="Rc451bd639c4e40fa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L271" r:id="R3ffb8e2a01b34b13"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="R6ba70d09f5534cad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L272" r:id="Re5e0d762603b4cdd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="R8d15a659b04a4bfa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L273" r:id="Rea33381d76cb4ea4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="Re17c0f7f54a94c7c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L274" r:id="Rfad30b2a37f543a3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="R94c33763bdec48e7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L275" r:id="R3dbb1678400348b6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O275" r:id="Rf50d9bba1f0c4293"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L276" r:id="Ra5618333706f4ee6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O276" r:id="R5dd8f38cb6e148aa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L277" r:id="Rde34878f99a14637"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O277" r:id="R433a7fa0d1f44083"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L278" r:id="Rb0783971540547f6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O278" r:id="R831f2744777040d1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L279" r:id="R81ee31686b754fad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="Rfa866938988c4761"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L280" r:id="R55dcbc6392504ed7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O280" r:id="Re7aa98ede8e6472a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L281" r:id="R3c59818fcda9412e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O281" r:id="R6691924a18584ff5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L282" r:id="Rd2aca0be11ff4c7b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O282" r:id="R32326787704549f2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L283" r:id="R80f53e0bb194475c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O283" r:id="R8b3f105dad0d4d30"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L284" r:id="R5a7c1d7c670b4692"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O284" r:id="R327661e9b08c4de7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L285" r:id="R24a4f2490a9649b4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="R68baceacb06f4e8b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L286" r:id="R5972770e37be4bc3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="Rb6e64dac5c4347a8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L287" r:id="R0a1b7a65bbd54000"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="R4dd99e82860641ef"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L288" r:id="Rfe729785e1e84a88"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="Rbe58a6e8e6be4640"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L289" r:id="R090b0bb31dcd4892"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="Rdbe3522cc24243e8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L290" r:id="R222e084450ef4fb3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="R754d9cbe6a774128"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L291" r:id="R02a2933870a1424b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="R86fcdeb5bc484b1f"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc2b2d1d41b9420d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ec88ac24a3a481f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
